--- a/DMX Board/Project Outputs for DMX Interface DB v2/BOM/Active BOM-DMX Interface(Production).xlsx
+++ b/DMX Board/Project Outputs for DMX Interface DB v2/BOM/Active BOM-DMX Interface(Production).xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\phil\Documents\code\dmx_interface_dev_board_v2\DMX Board\Project Outputs for DMX Interface DB v2\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{59672ADA-F621-4386-BF11-3CB41006B809}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D49059D9-F963-41FD-8D9C-F50DDDD2B48D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2120" yWindow="2580" windowWidth="31570" windowHeight="17480" xr2:uid="{B0515763-7F81-4224-B6E9-5859055C1290}"/>
+    <workbookView xWindow="2120" yWindow="2580" windowWidth="31570" windowHeight="17480" xr2:uid="{B48DD4B7-5067-43D3-9439-E4950D7751BD}"/>
   </bookViews>
   <sheets>
     <sheet name="Active BOM-DMX Interface(Produc" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="479" uniqueCount="346">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="346">
   <si>
     <t>JLCPN</t>
   </si>
@@ -854,19 +854,19 @@
     <t>CMP-009-00344-1</t>
   </si>
   <si>
+    <t>RC0603FR-0718KL</t>
+  </si>
+  <si>
+    <t>100mW Thick Film Resistors 75V ±100ppm/℃ ±1% 18kΩ 0603 Chip Resistor - Surface Mount ROHS</t>
+  </si>
+  <si>
+    <t>R37</t>
+  </si>
+  <si>
+    <t>CMP-009-00346-2</t>
+  </si>
+  <si>
     <t>C123417</t>
-  </si>
-  <si>
-    <t>RC0603FR-0718KL</t>
-  </si>
-  <si>
-    <t>100mW Thick Film Resistors 75V ±100ppm/℃ ±1% 18kΩ 0603 Chip Resistor - Surface Mount ROHS</t>
-  </si>
-  <si>
-    <t>R37</t>
-  </si>
-  <si>
-    <t>CMP-009-00346-1</t>
   </si>
   <si>
     <t>RC0603FR-0720KL</t>
@@ -1475,7 +1475,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1363688A-B26A-40B4-B731-E4E49FD90B72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{094384D2-3AE6-4D40-AFFE-134AEE6197F1}">
   <dimension ref="A1:K57"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2881,23 +2881,21 @@
       <c r="K44" s="1"/>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A45" s="2" t="s">
+      <c r="A45" s="1"/>
+      <c r="B45" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="B45" s="2" t="s">
+      <c r="C45" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="C45" s="2" t="s">
+      <c r="D45" s="2" t="s">
         <v>272</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>273</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>207</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G45" s="1">
         <v>1</v>
@@ -2909,7 +2907,7 @@
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>275</v>
